--- a/data/trans_orig/IP07C06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C06-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10910</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>21757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>39286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>22529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34565</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>34321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46780</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>59348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78036</t>
+          <t>78402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>25786</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23185</t>
+          <t>23656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23842</t>
+          <t>24505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60909</t>
+          <t>61154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74715</t>
+          <t>75290</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57592</t>
+          <t>57795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71117</t>
+          <t>71489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124413</t>
+          <t>124292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143299</t>
+          <t>143718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>30026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40624</t>
+          <t>41307</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34406</t>
+          <t>34347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45590</t>
+          <t>45924</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66930</t>
+          <t>67129</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83452</t>
+          <t>83085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20712</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>33756</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58199</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54876</t>
+          <t>55182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68948</t>
+          <t>69364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102079</t>
+          <t>103599</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122940</t>
+          <t>123499</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,46%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29049</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46385</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37058</t>
+          <t>36234</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>70051</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>97288</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>51439</t>
+          <t>51222</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>73525</t>
+          <t>72891</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59619</t>
+          <t>58512</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>94911</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>125630</t>
+          <t>126408</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>170047</t>
+          <t>170079</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196278</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>195584</t>
+          <t>196076</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>221918</t>
+          <t>221481</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>371172</t>
+          <t>370811</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>408075</t>
+          <t>408622</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>27273</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28326</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>41500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35995</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49783</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69131</t>
+          <t>67277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87866</t>
+          <t>87240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15268</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37976</t>
+          <t>37911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33112</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49586</t>
+          <t>49829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>44386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60057</t>
+          <t>60580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47749</t>
+          <t>48144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63625</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97359</t>
+          <t>96768</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118911</t>
+          <t>119088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13010</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26739</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33096</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>32975</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36526</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50068</t>
+          <t>48957</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72520</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>90836</t>
+          <t>91321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,47 +6548,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>7504</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2972</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>6809</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>25077</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43029</t>
+          <t>43751</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23827</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26339</t>
+          <t>26099</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28421</t>
+          <t>27292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46694</t>
+          <t>45875</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>39604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55653</t>
+          <t>55083</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39771</t>
+          <t>39448</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>55388</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>82183</t>
+          <t>83629</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>105559</t>
+          <t>106209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,0%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55820</t>
+          <t>56263</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>65195</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>85494</t>
+          <t>84654</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>116026</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>61425</t>
+          <t>61969</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>86353</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>73248</t>
+          <t>73308</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>117099</t>
+          <t>117436</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>150878</t>
+          <t>151131</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>159391</t>
+          <t>158722</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>188221</t>
+          <t>187007</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>174505</t>
+          <t>173440</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>203625</t>
+          <t>203531</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>342251</t>
+          <t>342725</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>384527</t>
+          <t>383667</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17035</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23891</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40639</t>
+          <t>40457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34515</t>
+          <t>35137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>48433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29126</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>43258</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68558</t>
+          <t>68458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87817</t>
+          <t>88791</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>27904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22969</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26720</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37563</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>39356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>59336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43088</t>
+          <t>43278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59570</t>
+          <t>59834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42047</t>
+          <t>41470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59577</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90499</t>
+          <t>89576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114099</t>
+          <t>113897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18713</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>22048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40058</t>
+          <t>40499</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>38173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50934</t>
+          <t>50425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42665</t>
+          <t>43419</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56961</t>
+          <t>57061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85496</t>
+          <t>86127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103986</t>
+          <t>104529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17972</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>17686</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32915</t>
+          <t>33633</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24490</t>
+          <t>24724</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33768</t>
+          <t>33898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53451</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53155</t>
+          <t>52843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70415</t>
+          <t>70128</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48870</t>
+          <t>48893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65149</t>
+          <t>65805</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>107680</t>
+          <t>108995</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>131813</t>
+          <t>131248</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>34161</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54815</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51946</t>
+          <t>52980</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>54533</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>70702</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>99276</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>55379</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>80223</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>76168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>104155</t>
+          <t>102962</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>139592</t>
+          <t>137332</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>176228</t>
+          <t>174457</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>184767</t>
+          <t>186369</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>214667</t>
+          <t>216364</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>177055</t>
+          <t>176833</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>210486</t>
+          <t>207611</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>374696</t>
+          <t>370732</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>415294</t>
+          <t>415043</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>
